--- a/TMD 450 region_hg38_hg19_Overall.xlsx
+++ b/TMD 450 region_hg38_hg19_Overall.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XN\du-an-dung-chung\Methyl-GW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XN\du-an-dung-chung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526119E2-E04F-4EED-93C1-8C7BA438B9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98EA6A7-1EED-45E4-93EB-72AE1756E868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CFF91632-3834-411B-933F-30A49CDBE6FA}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12638" uniqueCount="4346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12639" uniqueCount="4347">
   <si>
     <t>hg19</t>
   </si>
@@ -13080,6 +13080,9 @@
   </si>
   <si>
     <t>[nan, nan, nan, 'cg13601799', nan, nan, nan, nan, nan, nan, nan, nan, nan, nan]</t>
+  </si>
+  <si>
+    <t>MARCH11</t>
   </si>
 </sst>
 </file>
@@ -13121,18 +13124,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -13462,10 +13476,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C13D677-51B9-4FA8-8F43-26441F4E374A}">
-  <dimension ref="A1:K451"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K453"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.5703125" style="3" customWidth="1"/>
@@ -13546,7 +13561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -13581,7 +13596,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -13616,7 +13631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -13651,7 +13666,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -13686,7 +13701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -13721,7 +13736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -13756,7 +13771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -13791,7 +13806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -13826,7 +13841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -13861,7 +13876,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -13896,7 +13911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -13931,7 +13946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -13966,7 +13981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -14001,7 +14016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
@@ -14036,7 +14051,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -14071,7 +14086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>136</v>
       </c>
@@ -14106,7 +14121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>144</v>
       </c>
@@ -14141,7 +14156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -14176,7 +14191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>161</v>
       </c>
@@ -14211,7 +14226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>169</v>
       </c>
@@ -14246,7 +14261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>176</v>
       </c>
@@ -14281,42 +14296,42 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="H24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>3597</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="3" t="s">
         <v>3577</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>192</v>
       </c>
@@ -14351,7 +14366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>200</v>
       </c>
@@ -14386,7 +14401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>207</v>
       </c>
@@ -14421,7 +14436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>215</v>
       </c>
@@ -14456,7 +14471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>222</v>
       </c>
@@ -14491,7 +14506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>230</v>
       </c>
@@ -14526,7 +14541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>237</v>
       </c>
@@ -14561,7 +14576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>245</v>
       </c>
@@ -14596,7 +14611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>253</v>
       </c>
@@ -14631,7 +14646,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>261</v>
       </c>
@@ -14666,7 +14681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>269</v>
       </c>
@@ -14701,7 +14716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>277</v>
       </c>
@@ -14736,7 +14751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>285</v>
       </c>
@@ -14771,7 +14786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>293</v>
       </c>
@@ -14806,42 +14821,42 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="H39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>3625</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="3" t="s">
         <v>3577</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>309</v>
       </c>
@@ -14876,7 +14891,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>316</v>
       </c>
@@ -14911,7 +14926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>324</v>
       </c>
@@ -14946,7 +14961,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>331</v>
       </c>
@@ -14981,7 +14996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>339</v>
       </c>
@@ -15016,7 +15031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>346</v>
       </c>
@@ -15051,7 +15066,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>355</v>
       </c>
@@ -15086,7 +15101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>363</v>
       </c>
@@ -15121,7 +15136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>371</v>
       </c>
@@ -15156,7 +15171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>379</v>
       </c>
@@ -15191,42 +15206,42 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>388</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>3645</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="3" t="s">
         <v>3646</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>395</v>
       </c>
@@ -15261,7 +15276,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>403</v>
       </c>
@@ -15296,7 +15311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>411</v>
       </c>
@@ -15331,7 +15346,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>418</v>
       </c>
@@ -15366,7 +15381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>426</v>
       </c>
@@ -15401,7 +15416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>434</v>
       </c>
@@ -15436,7 +15451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>442</v>
       </c>
@@ -15471,42 +15486,42 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>451</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="H58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>3658</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="3" t="s">
         <v>3659</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>458</v>
       </c>
@@ -15541,7 +15556,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>465</v>
       </c>
@@ -15576,42 +15591,42 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>474</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="H61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>3664</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="3" t="s">
         <v>3665</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>481</v>
       </c>
@@ -15646,77 +15661,77 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>490</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="H63" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="H63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>3668</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="3" t="s">
         <v>3669</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="3">
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>498</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="H64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>3670</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="3" t="s">
         <v>3671</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>505</v>
       </c>
@@ -15751,7 +15766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>513</v>
       </c>
@@ -15786,7 +15801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>520</v>
       </c>
@@ -15821,7 +15836,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>528</v>
       </c>
@@ -15856,7 +15871,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>536</v>
       </c>
@@ -15891,7 +15906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>544</v>
       </c>
@@ -15926,7 +15941,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>552</v>
       </c>
@@ -15961,7 +15976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>560</v>
       </c>
@@ -15996,7 +16011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>568</v>
       </c>
@@ -16031,7 +16046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>575</v>
       </c>
@@ -16066,7 +16081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>583</v>
       </c>
@@ -16101,7 +16116,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>590</v>
       </c>
@@ -16136,7 +16151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>598</v>
       </c>
@@ -16171,7 +16186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>606</v>
       </c>
@@ -16206,7 +16221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>614</v>
       </c>
@@ -16241,7 +16256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>622</v>
       </c>
@@ -16276,7 +16291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>629</v>
       </c>
@@ -16311,7 +16326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>635</v>
       </c>
@@ -16346,7 +16361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>642</v>
       </c>
@@ -16381,7 +16396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>650</v>
       </c>
@@ -16416,7 +16431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>657</v>
       </c>
@@ -16451,7 +16466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>665</v>
       </c>
@@ -16486,7 +16501,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>673</v>
       </c>
@@ -16521,7 +16536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>681</v>
       </c>
@@ -16556,42 +16571,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
         <v>690</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
+      <c r="H89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>3716</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="3" t="s">
         <v>3717</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>697</v>
       </c>
@@ -16626,7 +16641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>705</v>
       </c>
@@ -16661,42 +16676,42 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="92" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
         <v>714</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="H92" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="H92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>3722</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J92" s="3" t="s">
         <v>3723</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>721</v>
       </c>
@@ -16731,7 +16746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>729</v>
       </c>
@@ -16766,7 +16781,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>737</v>
       </c>
@@ -16801,7 +16816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>745</v>
       </c>
@@ -16836,7 +16851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>754</v>
       </c>
@@ -16871,7 +16886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>762</v>
       </c>
@@ -16906,7 +16921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>770</v>
       </c>
@@ -16941,7 +16956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>777</v>
       </c>
@@ -16976,7 +16991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>784</v>
       </c>
@@ -17011,7 +17026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>792</v>
       </c>
@@ -17046,7 +17061,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>800</v>
       </c>
@@ -17081,7 +17096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>808</v>
       </c>
@@ -17116,7 +17131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>815</v>
       </c>
@@ -17151,7 +17166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>823</v>
       </c>
@@ -17186,7 +17201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>831</v>
       </c>
@@ -17221,42 +17236,42 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="108" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="3" t="s">
         <v>840</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I108" t="s">
+      <c r="I108" s="3" t="s">
         <v>3752</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J108" s="3" t="s">
         <v>3753</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>847</v>
       </c>
@@ -17291,7 +17306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>855</v>
       </c>
@@ -17326,7 +17341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>863</v>
       </c>
@@ -17361,7 +17376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>871</v>
       </c>
@@ -17396,7 +17411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>878</v>
       </c>
@@ -17431,7 +17446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>886</v>
       </c>
@@ -17466,7 +17481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>893</v>
       </c>
@@ -17501,7 +17516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>900</v>
       </c>
@@ -17536,7 +17551,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>908</v>
       </c>
@@ -17571,7 +17586,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>916</v>
       </c>
@@ -17606,7 +17621,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>924</v>
       </c>
@@ -17641,7 +17656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>932</v>
       </c>
@@ -17676,7 +17691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>940</v>
       </c>
@@ -17711,7 +17726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>948</v>
       </c>
@@ -17746,7 +17761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>956</v>
       </c>
@@ -17781,7 +17796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>963</v>
       </c>
@@ -17816,7 +17831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>972</v>
       </c>
@@ -17851,7 +17866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>980</v>
       </c>
@@ -17886,7 +17901,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>988</v>
       </c>
@@ -17921,7 +17936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>995</v>
       </c>
@@ -17956,7 +17971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1003</v>
       </c>
@@ -17991,7 +18006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1011</v>
       </c>
@@ -18026,42 +18041,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+    <row r="131" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="3" t="s">
         <v>1020</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>1021</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="3" t="s">
         <v>1022</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="H131" t="s">
-        <v>15</v>
-      </c>
-      <c r="I131" t="s">
+      <c r="H131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I131" s="3" t="s">
         <v>3793</v>
       </c>
-      <c r="J131" t="s">
+      <c r="J131" s="3" t="s">
         <v>3794</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1027</v>
       </c>
@@ -18096,7 +18111,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1035</v>
       </c>
@@ -18131,7 +18146,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1042</v>
       </c>
@@ -18166,7 +18181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1050</v>
       </c>
@@ -18201,7 +18216,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1058</v>
       </c>
@@ -18236,7 +18251,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1066</v>
       </c>
@@ -18271,77 +18286,77 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+    <row r="138" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="3" t="s">
         <v>1070</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="3" t="s">
         <v>1075</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="3" t="s">
         <v>1070</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G138" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="H138" t="s">
-        <v>15</v>
-      </c>
-      <c r="I138" t="s">
+      <c r="H138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>3807</v>
       </c>
-      <c r="J138" t="s">
+      <c r="J138" s="3" t="s">
         <v>3563</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+    <row r="139" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="3" t="s">
         <v>1083</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="G139" t="s">
+      <c r="G139" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="H139" t="s">
-        <v>15</v>
-      </c>
-      <c r="I139" t="s">
+      <c r="H139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" s="3" t="s">
         <v>3808</v>
       </c>
-      <c r="J139" t="s">
+      <c r="J139" s="3" t="s">
         <v>3809</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1091</v>
       </c>
@@ -18376,7 +18391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1099</v>
       </c>
@@ -18411,7 +18426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1107</v>
       </c>
@@ -18446,7 +18461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1115</v>
       </c>
@@ -18481,42 +18496,42 @@
         <v>56</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+    <row r="144" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="3" t="s">
         <v>1116</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F144" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="G144" t="s">
+      <c r="G144" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="H144" t="s">
+      <c r="H144" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I144" t="s">
+      <c r="I144" s="3" t="s">
         <v>3816</v>
       </c>
-      <c r="J144" t="s">
+      <c r="J144" s="3" t="s">
         <v>3817</v>
       </c>
-      <c r="K144">
+      <c r="K144" s="3">
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1130</v>
       </c>
@@ -18551,7 +18566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1138</v>
       </c>
@@ -18586,7 +18601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1146</v>
       </c>
@@ -18621,7 +18636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1154</v>
       </c>
@@ -18656,7 +18671,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1161</v>
       </c>
@@ -18691,7 +18706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1169</v>
       </c>
@@ -18726,7 +18741,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1177</v>
       </c>
@@ -18761,7 +18776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1185</v>
       </c>
@@ -18796,7 +18811,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1193</v>
       </c>
@@ -18831,7 +18846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1201</v>
       </c>
@@ -18866,7 +18881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1210</v>
       </c>
@@ -18901,7 +18916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1218</v>
       </c>
@@ -18936,7 +18951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1226</v>
       </c>
@@ -18971,7 +18986,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1234</v>
       </c>
@@ -19006,7 +19021,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1241</v>
       </c>
@@ -19041,7 +19056,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1248</v>
       </c>
@@ -19076,7 +19091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1256</v>
       </c>
@@ -19111,7 +19126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1264</v>
       </c>
@@ -19146,7 +19161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1272</v>
       </c>
@@ -19181,7 +19196,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1281</v>
       </c>
@@ -19216,7 +19231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1289</v>
       </c>
@@ -19251,7 +19266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1296</v>
       </c>
@@ -19286,7 +19301,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1304</v>
       </c>
@@ -19321,7 +19336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1312</v>
       </c>
@@ -19356,7 +19371,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1320</v>
       </c>
@@ -19391,7 +19406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>1328</v>
       </c>
@@ -19426,7 +19441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1336</v>
       </c>
@@ -19461,7 +19476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1344</v>
       </c>
@@ -19496,7 +19511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1352</v>
       </c>
@@ -19531,7 +19546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1359</v>
       </c>
@@ -19566,7 +19581,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1367</v>
       </c>
@@ -19601,7 +19616,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>1375</v>
       </c>
@@ -19636,7 +19651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1384</v>
       </c>
@@ -19671,7 +19686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1392</v>
       </c>
@@ -19706,7 +19721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1399</v>
       </c>
@@ -19741,7 +19756,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1407</v>
       </c>
@@ -19776,7 +19791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1415</v>
       </c>
@@ -19811,7 +19826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1423</v>
       </c>
@@ -19846,7 +19861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1431</v>
       </c>
@@ -19881,42 +19896,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="184" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="3" t="s">
         <v>1439</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>1440</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="F184" t="s">
+      <c r="F184" s="3" t="s">
         <v>1441</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="H184" t="s">
-        <v>15</v>
-      </c>
-      <c r="I184" t="s">
+      <c r="H184" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I184" s="3" t="s">
         <v>3883</v>
       </c>
-      <c r="J184" t="s">
+      <c r="J184" s="3" t="s">
         <v>3884</v>
       </c>
-      <c r="K184">
+      <c r="K184" s="3">
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1446</v>
       </c>
@@ -19951,7 +19966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1454</v>
       </c>
@@ -19986,7 +20001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1462</v>
       </c>
@@ -20021,7 +20036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1470</v>
       </c>
@@ -20056,7 +20071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1478</v>
       </c>
@@ -20091,7 +20106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1486</v>
       </c>
@@ -20126,42 +20141,42 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+    <row r="191" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="3" t="s">
         <v>1494</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F191" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G191" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="H191" t="s">
-        <v>15</v>
-      </c>
-      <c r="I191" t="s">
+      <c r="H191" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I191" s="3" t="s">
         <v>3896</v>
       </c>
-      <c r="J191" t="s">
+      <c r="J191" s="3" t="s">
         <v>3897</v>
       </c>
-      <c r="K191">
+      <c r="K191" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1501</v>
       </c>
@@ -20196,7 +20211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1509</v>
       </c>
@@ -20231,7 +20246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1516</v>
       </c>
@@ -20266,7 +20281,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1524</v>
       </c>
@@ -20301,7 +20316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1532</v>
       </c>
@@ -20336,7 +20351,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1540</v>
       </c>
@@ -20371,7 +20386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1548</v>
       </c>
@@ -20406,42 +20421,42 @@
         <v>26</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+    <row r="199" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="3" t="s">
         <v>1552</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="3" t="s">
         <v>1557</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>1558</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="3" t="s">
         <v>1552</v>
       </c>
-      <c r="F199" t="s">
+      <c r="F199" s="3" t="s">
         <v>1559</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="H199" t="s">
-        <v>15</v>
-      </c>
-      <c r="I199" t="s">
+      <c r="H199" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I199" s="3" t="s">
         <v>3910</v>
       </c>
-      <c r="J199" t="s">
+      <c r="J199" s="3" t="s">
         <v>3911</v>
       </c>
-      <c r="K199">
+      <c r="K199" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1564</v>
       </c>
@@ -20476,7 +20491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1572</v>
       </c>
@@ -20511,7 +20526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1580</v>
       </c>
@@ -20546,7 +20561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1588</v>
       </c>
@@ -20581,7 +20596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1596</v>
       </c>
@@ -20616,7 +20631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1605</v>
       </c>
@@ -20651,7 +20666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1612</v>
       </c>
@@ -20686,7 +20701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1620</v>
       </c>
@@ -20721,42 +20736,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+    <row r="208" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
         <v>1628</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="3" t="s">
         <v>1624</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="3" t="s">
         <v>1629</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>1630</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="3" t="s">
         <v>1624</v>
       </c>
-      <c r="F208" t="s">
+      <c r="F208" s="3" t="s">
         <v>1631</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="3" t="s">
         <v>1628</v>
       </c>
-      <c r="H208" t="s">
-        <v>15</v>
-      </c>
-      <c r="I208" t="s">
+      <c r="H208" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I208" s="3" t="s">
         <v>3925</v>
       </c>
-      <c r="J208" t="s">
+      <c r="J208" s="3" t="s">
         <v>3926</v>
       </c>
-      <c r="K208">
+      <c r="K208" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1636</v>
       </c>
@@ -20791,7 +20806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1644</v>
       </c>
@@ -20826,7 +20841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1652</v>
       </c>
@@ -20861,7 +20876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1659</v>
       </c>
@@ -20896,7 +20911,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1667</v>
       </c>
@@ -20931,7 +20946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1675</v>
       </c>
@@ -20966,7 +20981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1683</v>
       </c>
@@ -21001,7 +21016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1691</v>
       </c>
@@ -21036,7 +21051,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1699</v>
       </c>
@@ -21071,7 +21086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1708</v>
       </c>
@@ -21106,7 +21121,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1715</v>
       </c>
@@ -21141,7 +21156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1723</v>
       </c>
@@ -21176,7 +21191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1730</v>
       </c>
@@ -21211,7 +21226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1738</v>
       </c>
@@ -21246,7 +21261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1746</v>
       </c>
@@ -21281,42 +21296,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+    <row r="224" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
         <v>1754</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="3" t="s">
         <v>1755</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>1756</v>
       </c>
-      <c r="E224" t="s">
+      <c r="E224" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F224" s="3" t="s">
         <v>1757</v>
       </c>
-      <c r="G224" t="s">
+      <c r="G224" s="3" t="s">
         <v>1754</v>
       </c>
-      <c r="H224" t="s">
-        <v>15</v>
-      </c>
-      <c r="I224" t="s">
+      <c r="H224" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I224" s="3" t="s">
         <v>3949</v>
       </c>
-      <c r="J224" t="s">
+      <c r="J224" s="3" t="s">
         <v>3950</v>
       </c>
-      <c r="K224">
+      <c r="K224" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1762</v>
       </c>
@@ -21351,7 +21366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1770</v>
       </c>
@@ -21386,42 +21401,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+    <row r="227" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="3" t="s">
         <v>1778</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="3" t="s">
         <v>1774</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="3" t="s">
         <v>1771</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>1779</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="3" t="s">
         <v>1774</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="3" t="s">
         <v>1780</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G227" s="3" t="s">
         <v>1778</v>
       </c>
-      <c r="H227" t="s">
-        <v>15</v>
-      </c>
-      <c r="I227" t="s">
+      <c r="H227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I227" s="3" t="s">
         <v>3954</v>
       </c>
-      <c r="J227" t="s">
+      <c r="J227" s="3" t="s">
         <v>3955</v>
       </c>
-      <c r="K227">
+      <c r="K227" s="3">
         <v>27</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1785</v>
       </c>
@@ -21456,42 +21471,42 @@
         <v>29</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+    <row r="229" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="3" t="s">
         <v>1789</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="3" t="s">
         <v>1794</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>1795</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="3" t="s">
         <v>1789</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F229" s="3" t="s">
         <v>1796</v>
       </c>
-      <c r="G229" t="s">
+      <c r="G229" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="H229" t="s">
-        <v>15</v>
-      </c>
-      <c r="I229" t="s">
+      <c r="H229" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I229" s="3" t="s">
         <v>3958</v>
       </c>
-      <c r="J229" t="s">
+      <c r="J229" s="3" t="s">
         <v>3650</v>
       </c>
-      <c r="K229">
+      <c r="K229" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1801</v>
       </c>
@@ -21526,7 +21541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1808</v>
       </c>
@@ -21561,7 +21576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1816</v>
       </c>
@@ -21596,7 +21611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1823</v>
       </c>
@@ -21631,7 +21646,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1831</v>
       </c>
@@ -21666,7 +21681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1839</v>
       </c>
@@ -21701,7 +21716,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1847</v>
       </c>
@@ -21736,7 +21751,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1855</v>
       </c>
@@ -21771,7 +21786,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1863</v>
       </c>
@@ -21806,7 +21821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1871</v>
       </c>
@@ -21841,7 +21856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1879</v>
       </c>
@@ -21876,7 +21891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1887</v>
       </c>
@@ -21911,7 +21926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1894</v>
       </c>
@@ -21946,7 +21961,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1901</v>
       </c>
@@ -21981,7 +21996,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1909</v>
       </c>
@@ -22016,7 +22031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1917</v>
       </c>
@@ -22051,42 +22066,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+    <row r="246" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="s">
         <v>1925</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="3" t="s">
         <v>1921</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C246" s="3" t="s">
         <v>1926</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>1927</v>
       </c>
-      <c r="E246" t="s">
+      <c r="E246" s="3" t="s">
         <v>1921</v>
       </c>
-      <c r="F246" t="s">
+      <c r="F246" s="3" t="s">
         <v>1928</v>
       </c>
-      <c r="G246" t="s">
+      <c r="G246" s="3" t="s">
         <v>1925</v>
       </c>
-      <c r="H246" t="s">
-        <v>15</v>
-      </c>
-      <c r="I246" t="s">
+      <c r="H246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I246" s="3" t="s">
         <v>3989</v>
       </c>
-      <c r="J246" t="s">
+      <c r="J246" s="3" t="s">
         <v>3990</v>
       </c>
-      <c r="K246">
+      <c r="K246" s="3">
         <v>48</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1933</v>
       </c>
@@ -22121,42 +22136,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+    <row r="248" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
         <v>1941</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="3" t="s">
         <v>1937</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C248" s="3" t="s">
         <v>1942</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>1943</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E248" s="3" t="s">
         <v>1937</v>
       </c>
-      <c r="F248" t="s">
+      <c r="F248" s="3" t="s">
         <v>1944</v>
       </c>
-      <c r="G248" t="s">
+      <c r="G248" s="3" t="s">
         <v>1941</v>
       </c>
-      <c r="H248" t="s">
-        <v>15</v>
-      </c>
-      <c r="I248" t="s">
+      <c r="H248" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I248" s="3" t="s">
         <v>3993</v>
       </c>
-      <c r="J248" t="s">
+      <c r="J248" s="3" t="s">
         <v>3994</v>
       </c>
-      <c r="K248">
+      <c r="K248" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1949</v>
       </c>
@@ -22191,7 +22206,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1957</v>
       </c>
@@ -22226,7 +22241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1965</v>
       </c>
@@ -22261,7 +22276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1973</v>
       </c>
@@ -22296,7 +22311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1981</v>
       </c>
@@ -22331,7 +22346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1989</v>
       </c>
@@ -22366,7 +22381,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1997</v>
       </c>
@@ -22401,7 +22416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>2005</v>
       </c>
@@ -22436,77 +22451,77 @@
         <v>23</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+    <row r="257" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
         <v>2013</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="3" t="s">
         <v>2009</v>
       </c>
-      <c r="C257" t="s">
+      <c r="C257" s="3" t="s">
         <v>2014</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>2015</v>
       </c>
-      <c r="E257" t="s">
+      <c r="E257" s="3" t="s">
         <v>2009</v>
       </c>
-      <c r="F257" t="s">
+      <c r="F257" s="3" t="s">
         <v>2016</v>
       </c>
-      <c r="G257" t="s">
+      <c r="G257" s="3" t="s">
         <v>2013</v>
       </c>
-      <c r="H257" t="s">
-        <v>15</v>
-      </c>
-      <c r="I257" t="s">
+      <c r="H257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I257" s="3" t="s">
         <v>4010</v>
       </c>
-      <c r="J257" t="s">
+      <c r="J257" s="3" t="s">
         <v>4011</v>
       </c>
-      <c r="K257">
+      <c r="K257" s="3">
         <v>61</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+    <row r="258" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="3" t="s">
         <v>2017</v>
       </c>
-      <c r="C258" t="s">
+      <c r="C258" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>2023</v>
       </c>
-      <c r="E258" t="s">
+      <c r="E258" s="3" t="s">
         <v>2017</v>
       </c>
-      <c r="F258" t="s">
+      <c r="F258" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="G258" t="s">
+      <c r="G258" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="H258" t="s">
-        <v>15</v>
-      </c>
-      <c r="I258" t="s">
+      <c r="H258" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I258" s="3" t="s">
         <v>4012</v>
       </c>
-      <c r="J258" t="s">
+      <c r="J258" s="3" t="s">
         <v>4013</v>
       </c>
-      <c r="K258">
+      <c r="K258" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>2029</v>
       </c>
@@ -22541,7 +22556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>2037</v>
       </c>
@@ -22576,7 +22591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>2045</v>
       </c>
@@ -22611,7 +22626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>2052</v>
       </c>
@@ -22646,7 +22661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>2060</v>
       </c>
@@ -22681,7 +22696,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>2068</v>
       </c>
@@ -22716,7 +22731,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>2076</v>
       </c>
@@ -22751,7 +22766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>2084</v>
       </c>
@@ -22786,7 +22801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>2091</v>
       </c>
@@ -22821,7 +22836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>2099</v>
       </c>
@@ -22856,7 +22871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>2107</v>
       </c>
@@ -22891,7 +22906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>2116</v>
       </c>
@@ -22926,7 +22941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>2124</v>
       </c>
@@ -22961,7 +22976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>2132</v>
       </c>
@@ -22996,7 +23011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>2140</v>
       </c>
@@ -23031,7 +23046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>2148</v>
       </c>
@@ -23066,7 +23081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>2156</v>
       </c>
@@ -23101,7 +23116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>2164</v>
       </c>
@@ -23136,7 +23151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>2173</v>
       </c>
@@ -23171,7 +23186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>2181</v>
       </c>
@@ -23206,7 +23221,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>2188</v>
       </c>
@@ -23241,7 +23256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>2196</v>
       </c>
@@ -23276,7 +23291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>2205</v>
       </c>
@@ -23311,7 +23326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>2213</v>
       </c>
@@ -23346,7 +23361,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>2220</v>
       </c>
@@ -23381,7 +23396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>2228</v>
       </c>
@@ -23416,7 +23431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>2236</v>
       </c>
@@ -23451,7 +23466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>2244</v>
       </c>
@@ -23486,7 +23501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>2252</v>
       </c>
@@ -23521,7 +23536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>2260</v>
       </c>
@@ -23556,7 +23571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>2268</v>
       </c>
@@ -23591,7 +23606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>2276</v>
       </c>
@@ -23626,7 +23641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>2284</v>
       </c>
@@ -23661,7 +23676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>2293</v>
       </c>
@@ -23696,7 +23711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>2301</v>
       </c>
@@ -23731,7 +23746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>2309</v>
       </c>
@@ -23766,7 +23781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>2317</v>
       </c>
@@ -23801,7 +23816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>2325</v>
       </c>
@@ -23836,7 +23851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>2333</v>
       </c>
@@ -23871,7 +23886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>2341</v>
       </c>
@@ -23906,7 +23921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>2349</v>
       </c>
@@ -23941,7 +23956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>2356</v>
       </c>
@@ -23976,7 +23991,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>2364</v>
       </c>
@@ -24011,7 +24026,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>2372</v>
       </c>
@@ -24046,7 +24061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>2380</v>
       </c>
@@ -24081,7 +24096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>2387</v>
       </c>
@@ -24116,7 +24131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>2395</v>
       </c>
@@ -24151,7 +24166,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>2403</v>
       </c>
@@ -24186,7 +24201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>2411</v>
       </c>
@@ -24221,7 +24236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>2418</v>
       </c>
@@ -24256,7 +24271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>2427</v>
       </c>
@@ -24291,7 +24306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>2435</v>
       </c>
@@ -24326,7 +24341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>2443</v>
       </c>
@@ -24361,7 +24376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>2451</v>
       </c>
@@ -24396,7 +24411,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>2458</v>
       </c>
@@ -24431,42 +24446,42 @@
         <v>34</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+    <row r="314" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
         <v>2466</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="3" t="s">
         <v>2462</v>
       </c>
-      <c r="C314" t="s">
+      <c r="C314" s="3" t="s">
         <v>2467</v>
       </c>
       <c r="D314" s="3" t="s">
         <v>2468</v>
       </c>
-      <c r="E314" t="s">
+      <c r="E314" s="3" t="s">
         <v>2462</v>
       </c>
-      <c r="F314" t="s">
+      <c r="F314" s="3" t="s">
         <v>2469</v>
       </c>
-      <c r="G314" t="s">
+      <c r="G314" s="3" t="s">
         <v>2466</v>
       </c>
-      <c r="H314" t="s">
-        <v>15</v>
-      </c>
-      <c r="I314" t="s">
+      <c r="H314" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I314" s="3" t="s">
         <v>4111</v>
       </c>
-      <c r="J314" t="s">
+      <c r="J314" s="3" t="s">
         <v>4112</v>
       </c>
-      <c r="K314">
+      <c r="K314" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>2474</v>
       </c>
@@ -24501,7 +24516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>2482</v>
       </c>
@@ -24536,7 +24551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>2489</v>
       </c>
@@ -24571,7 +24586,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>2497</v>
       </c>
@@ -24606,7 +24621,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>2505</v>
       </c>
@@ -24641,42 +24656,42 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+    <row r="320" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="3" t="s">
         <v>2509</v>
       </c>
-      <c r="C320" t="s">
+      <c r="C320" s="3" t="s">
         <v>2514</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>2515</v>
       </c>
-      <c r="E320" t="s">
+      <c r="E320" s="3" t="s">
         <v>2509</v>
       </c>
-      <c r="F320" t="s">
+      <c r="F320" s="3" t="s">
         <v>2516</v>
       </c>
-      <c r="G320" t="s">
+      <c r="G320" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="H320" t="s">
-        <v>15</v>
-      </c>
-      <c r="I320" t="s">
+      <c r="H320" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I320" s="3" t="s">
         <v>4122</v>
       </c>
-      <c r="J320" t="s">
+      <c r="J320" s="3" t="s">
         <v>3798</v>
       </c>
-      <c r="K320">
+      <c r="K320" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>2521</v>
       </c>
@@ -24711,7 +24726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>2529</v>
       </c>
@@ -24746,7 +24761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>2537</v>
       </c>
@@ -24781,7 +24796,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>2545</v>
       </c>
@@ -24816,7 +24831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>2553</v>
       </c>
@@ -24851,42 +24866,42 @@
         <v>18</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
+    <row r="326" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
         <v>2561</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="3" t="s">
         <v>2557</v>
       </c>
-      <c r="C326" t="s">
+      <c r="C326" s="3" t="s">
         <v>2562</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>2563</v>
       </c>
-      <c r="E326" t="s">
+      <c r="E326" s="3" t="s">
         <v>2557</v>
       </c>
-      <c r="F326" t="s">
+      <c r="F326" s="3" t="s">
         <v>2564</v>
       </c>
-      <c r="G326" t="s">
+      <c r="G326" s="3" t="s">
         <v>2561</v>
       </c>
-      <c r="H326" t="s">
-        <v>15</v>
-      </c>
-      <c r="I326" t="s">
+      <c r="H326" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I326" s="3" t="s">
         <v>4132</v>
       </c>
-      <c r="J326" t="s">
+      <c r="J326" s="3" t="s">
         <v>4133</v>
       </c>
-      <c r="K326">
+      <c r="K326" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>2569</v>
       </c>
@@ -24921,7 +24936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>2577</v>
       </c>
@@ -24956,7 +24971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>2585</v>
       </c>
@@ -24991,42 +25006,42 @@
         <v>13</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+    <row r="330" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="3" t="s">
         <v>2588</v>
       </c>
-      <c r="C330" t="s">
+      <c r="C330" s="3" t="s">
         <v>2593</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>2594</v>
       </c>
-      <c r="E330" t="s">
+      <c r="E330" s="3" t="s">
         <v>2588</v>
       </c>
-      <c r="F330" t="s">
+      <c r="F330" s="3" t="s">
         <v>2595</v>
       </c>
-      <c r="G330" t="s">
+      <c r="G330" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="H330" t="s">
+      <c r="H330" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I330" t="s">
+      <c r="I330" s="3" t="s">
         <v>4138</v>
       </c>
-      <c r="J330" t="s">
+      <c r="J330" s="3" t="s">
         <v>4139</v>
       </c>
-      <c r="K330">
+      <c r="K330" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>2600</v>
       </c>
@@ -25061,7 +25076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>2609</v>
       </c>
@@ -25096,7 +25111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>2617</v>
       </c>
@@ -25131,7 +25146,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>2624</v>
       </c>
@@ -25166,7 +25181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>2632</v>
       </c>
@@ -25201,42 +25216,42 @@
         <v>24</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
+    <row r="336" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="3" t="s">
         <v>2640</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="3" t="s">
         <v>2636</v>
       </c>
-      <c r="C336" s="1">
-        <v>45727</v>
+      <c r="C336" s="5" t="s">
+        <v>4346</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>2641</v>
       </c>
-      <c r="E336" t="s">
+      <c r="E336" s="3" t="s">
         <v>2636</v>
       </c>
-      <c r="F336" t="s">
+      <c r="F336" s="3" t="s">
         <v>2642</v>
       </c>
-      <c r="G336" t="s">
+      <c r="G336" s="3" t="s">
         <v>2640</v>
       </c>
-      <c r="H336" t="s">
+      <c r="H336" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I336" t="s">
+      <c r="I336" s="3" t="s">
         <v>4150</v>
       </c>
-      <c r="J336" t="s">
+      <c r="J336" s="3" t="s">
         <v>4151</v>
       </c>
-      <c r="K336">
+      <c r="K336" s="3">
         <v>61</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>2647</v>
       </c>
@@ -25271,7 +25286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>2655</v>
       </c>
@@ -25306,7 +25321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>2663</v>
       </c>
@@ -25341,7 +25356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>2671</v>
       </c>
@@ -25376,7 +25391,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>2679</v>
       </c>
@@ -25411,7 +25426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>2687</v>
       </c>
@@ -25446,7 +25461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>2695</v>
       </c>
@@ -25481,7 +25496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>2703</v>
       </c>
@@ -25516,7 +25531,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>2711</v>
       </c>
@@ -25551,7 +25566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2719</v>
       </c>
@@ -25586,7 +25601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>2727</v>
       </c>
@@ -25621,7 +25636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>2735</v>
       </c>
@@ -25656,7 +25671,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2743</v>
       </c>
@@ -25691,7 +25706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>2751</v>
       </c>
@@ -25726,7 +25741,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2759</v>
       </c>
@@ -25761,7 +25776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>2767</v>
       </c>
@@ -25796,7 +25811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>2776</v>
       </c>
@@ -25831,7 +25846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2784</v>
       </c>
@@ -25866,7 +25881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2792</v>
       </c>
@@ -25901,7 +25916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2800</v>
       </c>
@@ -25936,7 +25951,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2808</v>
       </c>
@@ -25971,7 +25986,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>2816</v>
       </c>
@@ -26006,7 +26021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>2824</v>
       </c>
@@ -26041,7 +26056,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>2832</v>
       </c>
@@ -26076,7 +26091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>2840</v>
       </c>
@@ -26111,7 +26126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>2848</v>
       </c>
@@ -26146,7 +26161,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>2856</v>
       </c>
@@ -26181,7 +26196,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>2864</v>
       </c>
@@ -26216,42 +26231,42 @@
         <v>71</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
+    <row r="365" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="C365" t="s">
+      <c r="C365" s="3" t="s">
         <v>2873</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>2874</v>
       </c>
-      <c r="E365" t="s">
+      <c r="E365" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="F365" t="s">
+      <c r="F365" s="3" t="s">
         <v>2875</v>
       </c>
-      <c r="G365" t="s">
+      <c r="G365" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="H365" t="s">
-        <v>15</v>
-      </c>
-      <c r="I365" t="s">
+      <c r="H365" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I365" s="3" t="s">
         <v>4205</v>
       </c>
-      <c r="J365" t="s">
+      <c r="J365" s="3" t="s">
         <v>4206</v>
       </c>
-      <c r="K365">
+      <c r="K365" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>2880</v>
       </c>
@@ -26286,7 +26301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>2888</v>
       </c>
@@ -26321,42 +26336,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
+    <row r="368" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="3" t="s">
         <v>2896</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="3" t="s">
         <v>2892</v>
       </c>
-      <c r="C368" t="s">
+      <c r="C368" s="3" t="s">
         <v>2889</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>2897</v>
       </c>
-      <c r="E368" t="s">
+      <c r="E368" s="3" t="s">
         <v>2892</v>
       </c>
-      <c r="F368" t="s">
+      <c r="F368" s="3" t="s">
         <v>2898</v>
       </c>
-      <c r="G368" t="s">
+      <c r="G368" s="3" t="s">
         <v>2896</v>
       </c>
-      <c r="H368" t="s">
+      <c r="H368" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I368" t="s">
+      <c r="I368" s="3" t="s">
         <v>4210</v>
       </c>
-      <c r="J368" t="s">
+      <c r="J368" s="3" t="s">
         <v>4211</v>
       </c>
-      <c r="K368">
+      <c r="K368" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>2903</v>
       </c>
@@ -26391,42 +26406,42 @@
         <v>31</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
+    <row r="370" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="3" t="s">
         <v>2911</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="3" t="s">
         <v>2907</v>
       </c>
-      <c r="C370" t="s">
+      <c r="C370" s="3" t="s">
         <v>2912</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>2913</v>
       </c>
-      <c r="E370" t="s">
+      <c r="E370" s="3" t="s">
         <v>2907</v>
       </c>
-      <c r="F370" t="s">
+      <c r="F370" s="3" t="s">
         <v>2914</v>
       </c>
-      <c r="G370" t="s">
+      <c r="G370" s="3" t="s">
         <v>2911</v>
       </c>
-      <c r="H370" t="s">
-        <v>15</v>
-      </c>
-      <c r="I370" t="s">
+      <c r="H370" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I370" s="3" t="s">
         <v>4214</v>
       </c>
-      <c r="J370" t="s">
+      <c r="J370" s="3" t="s">
         <v>4215</v>
       </c>
-      <c r="K370">
+      <c r="K370" s="3">
         <v>41</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>2919</v>
       </c>
@@ -26461,7 +26476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>2927</v>
       </c>
@@ -26496,7 +26511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>2934</v>
       </c>
@@ -26531,42 +26546,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
+    <row r="374" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="3" t="s">
         <v>2942</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="3" t="s">
         <v>2938</v>
       </c>
-      <c r="C374" t="s">
+      <c r="C374" s="3" t="s">
         <v>2943</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>2944</v>
       </c>
-      <c r="E374" t="s">
+      <c r="E374" s="3" t="s">
         <v>2938</v>
       </c>
-      <c r="F374" t="s">
+      <c r="F374" s="3" t="s">
         <v>2945</v>
       </c>
-      <c r="G374" t="s">
+      <c r="G374" s="3" t="s">
         <v>2942</v>
       </c>
-      <c r="H374" t="s">
-        <v>15</v>
-      </c>
-      <c r="I374" t="s">
+      <c r="H374" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I374" s="3" t="s">
         <v>4219</v>
       </c>
-      <c r="J374" t="s">
+      <c r="J374" s="3" t="s">
         <v>4220</v>
       </c>
-      <c r="K374">
+      <c r="K374" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>2950</v>
       </c>
@@ -26601,7 +26616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>2958</v>
       </c>
@@ -26636,42 +26651,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
+    <row r="377" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="3" t="s">
         <v>2967</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="3" t="s">
         <v>2962</v>
       </c>
-      <c r="C377" t="s">
+      <c r="C377" s="3" t="s">
         <v>2968</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>2969</v>
       </c>
-      <c r="E377" t="s">
+      <c r="E377" s="3" t="s">
         <v>2962</v>
       </c>
-      <c r="F377" t="s">
+      <c r="F377" s="3" t="s">
         <v>2970</v>
       </c>
-      <c r="G377" t="s">
+      <c r="G377" s="3" t="s">
         <v>2967</v>
       </c>
-      <c r="H377" t="s">
-        <v>15</v>
-      </c>
-      <c r="I377" t="s">
+      <c r="H377" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I377" s="3" t="s">
         <v>4225</v>
       </c>
-      <c r="J377" t="s">
+      <c r="J377" s="3" t="s">
         <v>3563</v>
       </c>
-      <c r="K377">
+      <c r="K377" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>2975</v>
       </c>
@@ -26706,7 +26721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2983</v>
       </c>
@@ -26741,7 +26756,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>2991</v>
       </c>
@@ -26776,7 +26791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>2999</v>
       </c>
@@ -26811,7 +26826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>3007</v>
       </c>
@@ -26846,7 +26861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>3015</v>
       </c>
@@ -26881,7 +26896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>3023</v>
       </c>
@@ -26916,7 +26931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>3031</v>
       </c>
@@ -26951,7 +26966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>3039</v>
       </c>
@@ -26986,7 +27001,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>3047</v>
       </c>
@@ -27021,7 +27036,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>3055</v>
       </c>
@@ -27056,7 +27071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>3062</v>
       </c>
@@ -27091,7 +27106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>3070</v>
       </c>
@@ -27126,7 +27141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>3078</v>
       </c>
@@ -27161,7 +27176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>3086</v>
       </c>
@@ -27196,42 +27211,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
+    <row r="393" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="3" t="s">
         <v>3094</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="3" t="s">
         <v>3090</v>
       </c>
-      <c r="C393" t="s">
+      <c r="C393" s="3" t="s">
         <v>3095</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>3096</v>
       </c>
-      <c r="E393" t="s">
+      <c r="E393" s="3" t="s">
         <v>3090</v>
       </c>
-      <c r="F393" t="s">
+      <c r="F393" s="3" t="s">
         <v>3097</v>
       </c>
-      <c r="G393" t="s">
+      <c r="G393" s="3" t="s">
         <v>3094</v>
       </c>
-      <c r="H393" t="s">
-        <v>15</v>
-      </c>
-      <c r="I393" t="s">
+      <c r="H393" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I393" s="3" t="s">
         <v>4251</v>
       </c>
-      <c r="J393" t="s">
+      <c r="J393" s="3" t="s">
         <v>3909</v>
       </c>
-      <c r="K393">
+      <c r="K393" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>3102</v>
       </c>
@@ -27266,7 +27281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>3109</v>
       </c>
@@ -27301,7 +27316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>3117</v>
       </c>
@@ -27336,7 +27351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>3124</v>
       </c>
@@ -27371,7 +27386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>3132</v>
       </c>
@@ -27406,7 +27421,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>3139</v>
       </c>
@@ -27441,7 +27456,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>3147</v>
       </c>
@@ -27476,7 +27491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>3155</v>
       </c>
@@ -27511,7 +27526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>3163</v>
       </c>
@@ -27546,7 +27561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>3171</v>
       </c>
@@ -27581,7 +27596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>3179</v>
       </c>
@@ -27616,7 +27631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>3186</v>
       </c>
@@ -27651,7 +27666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>3194</v>
       </c>
@@ -27686,42 +27701,42 @@
         <v>13</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
+    <row r="407" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="3" t="s">
         <v>3201</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B407" s="3" t="s">
         <v>3197</v>
       </c>
-      <c r="C407" t="s">
+      <c r="C407" s="3" t="s">
         <v>3202</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>3203</v>
       </c>
-      <c r="E407" t="s">
+      <c r="E407" s="3" t="s">
         <v>3197</v>
       </c>
-      <c r="F407" t="s">
+      <c r="F407" s="3" t="s">
         <v>3204</v>
       </c>
-      <c r="G407" t="s">
+      <c r="G407" s="3" t="s">
         <v>3201</v>
       </c>
-      <c r="H407" t="s">
+      <c r="H407" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I407" t="s">
+      <c r="I407" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="J407" t="s">
+      <c r="J407" s="3" t="s">
         <v>3755</v>
       </c>
-      <c r="K407">
+      <c r="K407" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>3209</v>
       </c>
@@ -27756,7 +27771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>3218</v>
       </c>
@@ -27791,7 +27806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>3226</v>
       </c>
@@ -27826,7 +27841,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>3233</v>
       </c>
@@ -27861,7 +27876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>3240</v>
       </c>
@@ -27896,7 +27911,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>3248</v>
       </c>
@@ -27931,7 +27946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>3256</v>
       </c>
@@ -27966,7 +27981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>3264</v>
       </c>
@@ -28001,7 +28016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>3272</v>
       </c>
@@ -28036,7 +28051,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>3280</v>
       </c>
@@ -28071,7 +28086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>3288</v>
       </c>
@@ -28106,7 +28121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>3296</v>
       </c>
@@ -28141,7 +28156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>3303</v>
       </c>
@@ -28176,7 +28191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>3311</v>
       </c>
@@ -28211,7 +28226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>3319</v>
       </c>
@@ -28246,7 +28261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>3327</v>
       </c>
@@ -28281,7 +28296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>3335</v>
       </c>
@@ -28316,7 +28331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>3343</v>
       </c>
@@ -28351,7 +28366,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>3351</v>
       </c>
@@ -28386,7 +28401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>3359</v>
       </c>
@@ -28421,7 +28436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>3367</v>
       </c>
@@ -28456,7 +28471,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>3375</v>
       </c>
@@ -28491,7 +28506,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>3383</v>
       </c>
@@ -28526,7 +28541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>3391</v>
       </c>
@@ -28561,7 +28576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>3398</v>
       </c>
@@ -28596,7 +28611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>3406</v>
       </c>
@@ -28631,42 +28646,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
+    <row r="434" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A434" s="3" t="s">
         <v>3415</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B434" s="3" t="s">
         <v>3410</v>
       </c>
-      <c r="C434" t="s">
+      <c r="C434" s="3" t="s">
         <v>3416</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>3410</v>
       </c>
-      <c r="E434" t="s">
+      <c r="E434" s="3" t="s">
         <v>3410</v>
       </c>
-      <c r="F434" t="s">
+      <c r="F434" s="3" t="s">
         <v>3417</v>
       </c>
-      <c r="G434" t="s">
+      <c r="G434" s="3" t="s">
         <v>3415</v>
       </c>
-      <c r="H434" t="s">
-        <v>15</v>
-      </c>
-      <c r="I434" t="s">
+      <c r="H434" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I434" s="3" t="s">
         <v>4319</v>
       </c>
-      <c r="J434" t="s">
+      <c r="J434" s="3" t="s">
         <v>4320</v>
       </c>
-      <c r="K434">
+      <c r="K434" s="3">
         <v>53</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>3422</v>
       </c>
@@ -28701,7 +28716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>3430</v>
       </c>
@@ -28736,7 +28751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>3438</v>
       </c>
@@ -28771,7 +28786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>3446</v>
       </c>
@@ -28806,7 +28821,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>3453</v>
       </c>
@@ -28841,7 +28856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>3461</v>
       </c>
@@ -28876,7 +28891,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>3469</v>
       </c>
@@ -28911,7 +28926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>3476</v>
       </c>
@@ -28946,7 +28961,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>3484</v>
       </c>
@@ -28981,7 +28996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>3492</v>
       </c>
@@ -29016,42 +29031,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
+    <row r="445" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A445" s="3" t="s">
         <v>3500</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="3" t="s">
         <v>3496</v>
       </c>
-      <c r="C445" t="s">
+      <c r="C445" s="3" t="s">
         <v>3501</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>3502</v>
       </c>
-      <c r="E445" t="s">
+      <c r="E445" s="3" t="s">
         <v>3496</v>
       </c>
-      <c r="F445" t="s">
+      <c r="F445" s="3" t="s">
         <v>3503</v>
       </c>
-      <c r="G445" t="s">
+      <c r="G445" s="3" t="s">
         <v>3500</v>
       </c>
-      <c r="H445" t="s">
-        <v>15</v>
-      </c>
-      <c r="I445" t="s">
+      <c r="H445" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I445" s="3" t="s">
         <v>4336</v>
       </c>
-      <c r="J445" t="s">
+      <c r="J445" s="3" t="s">
         <v>3796</v>
       </c>
-      <c r="K445">
+      <c r="K445" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>3508</v>
       </c>
@@ -29086,7 +29101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>3516</v>
       </c>
@@ -29121,7 +29136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>3523</v>
       </c>
@@ -29156,7 +29171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>3531</v>
       </c>
@@ -29191,7 +29206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>3539</v>
       </c>
@@ -29226,7 +29241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>3547</v>
       </c>
@@ -29261,8 +29276,15 @@
         <v>14</v>
       </c>
     </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E453" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K451" xr:uid="{6C13D677-51B9-4FA8-8F43-26441F4E374A}"/>
+  <autoFilter ref="A1:K451" xr:uid="{6C13D677-51B9-4FA8-8F43-26441F4E374A}">
+    <filterColumn colId="1">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
